--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_15-11-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_15-11-2025.xlsx
@@ -592,23 +592,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a31a235
-	0x7ff60a072650
-	0x7ff609e016dd
-	0x7ff609e5a27e
-	0x7ff609e5a58c
-	0x7ff609eaed77
-	0x7ff609eababa
-	0x7ff609e4b0ed
-	0x7ff609e4bf63
-	0x7ff60a345d60
-	0x7ff60a33fe8a
-	0x7ff60a361005
-	0x7ff60a08d73e
-	0x7ff60a094e3f
-	0x7ff60a07b7e4
-	0x7ff60a07b99f
-	0x7ff60a061908
+	0x7ff7747ba235
+	0x7ff774512650
+	0x7ff7742a16dd
+	0x7ff7742fa27e
+	0x7ff7742fa58c
+	0x7ff77434ed77
+	0x7ff77434baba
+	0x7ff7742eb0ed
+	0x7ff7742ebf63
+	0x7ff7747e5d60
+	0x7ff7747dfe8a
+	0x7ff774801005
+	0x7ff77452d73e
+	0x7ff774534e3f
+	0x7ff77451b7e4
+	0x7ff77451b99f
+	0x7ff774501908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -712,23 +712,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a31a235
-	0x7ff60a072650
-	0x7ff609e016dd
-	0x7ff609e5a27e
-	0x7ff609e5a58c
-	0x7ff609eaed77
-	0x7ff609eababa
-	0x7ff609e4b0ed
-	0x7ff609e4bf63
-	0x7ff60a345d60
-	0x7ff60a33fe8a
-	0x7ff60a361005
-	0x7ff60a08d73e
-	0x7ff60a094e3f
-	0x7ff60a07b7e4
-	0x7ff60a07b99f
-	0x7ff60a061908
+	0x7ff7747ba235
+	0x7ff774512650
+	0x7ff7742a16dd
+	0x7ff7742fa27e
+	0x7ff7742fa58c
+	0x7ff77434ed77
+	0x7ff77434baba
+	0x7ff7742eb0ed
+	0x7ff7742ebf63
+	0x7ff7747e5d60
+	0x7ff7747dfe8a
+	0x7ff774801005
+	0x7ff77452d73e
+	0x7ff774534e3f
+	0x7ff77451b7e4
+	0x7ff77451b99f
+	0x7ff774501908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -832,23 +832,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a31a235
-	0x7ff60a072650
-	0x7ff609e016dd
-	0x7ff609e5a27e
-	0x7ff609e5a58c
-	0x7ff609eaed77
-	0x7ff609eababa
-	0x7ff609e4b0ed
-	0x7ff609e4bf63
-	0x7ff60a345d60
-	0x7ff60a33fe8a
-	0x7ff60a361005
-	0x7ff60a08d73e
-	0x7ff60a094e3f
-	0x7ff60a07b7e4
-	0x7ff60a07b99f
-	0x7ff60a061908
+	0x7ff7747ba235
+	0x7ff774512650
+	0x7ff7742a16dd
+	0x7ff7742fa27e
+	0x7ff7742fa58c
+	0x7ff77434ed77
+	0x7ff77434baba
+	0x7ff7742eb0ed
+	0x7ff7742ebf63
+	0x7ff7747e5d60
+	0x7ff7747dfe8a
+	0x7ff774801005
+	0x7ff77452d73e
+	0x7ff774534e3f
+	0x7ff77451b7e4
+	0x7ff77451b99f
+	0x7ff774501908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -952,23 +952,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a31a235
-	0x7ff60a072650
-	0x7ff609e016dd
-	0x7ff609e5a27e
-	0x7ff609e5a58c
-	0x7ff609eaed77
-	0x7ff609eababa
-	0x7ff609e4b0ed
-	0x7ff609e4bf63
-	0x7ff60a345d60
-	0x7ff60a33fe8a
-	0x7ff60a361005
-	0x7ff60a08d73e
-	0x7ff60a094e3f
-	0x7ff60a07b7e4
-	0x7ff60a07b99f
-	0x7ff60a061908
+	0x7ff7747ba235
+	0x7ff774512650
+	0x7ff7742a16dd
+	0x7ff7742fa27e
+	0x7ff7742fa58c
+	0x7ff77434ed77
+	0x7ff77434baba
+	0x7ff7742eb0ed
+	0x7ff7742ebf63
+	0x7ff7747e5d60
+	0x7ff7747dfe8a
+	0x7ff774801005
+	0x7ff77452d73e
+	0x7ff774534e3f
+	0x7ff77451b7e4
+	0x7ff77451b99f
+	0x7ff774501908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1072,23 +1072,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a31a235
-	0x7ff60a072650
-	0x7ff609e016dd
-	0x7ff609e5a27e
-	0x7ff609e5a58c
-	0x7ff609eaed77
-	0x7ff609eababa
-	0x7ff609e4b0ed
-	0x7ff609e4bf63
-	0x7ff60a345d60
-	0x7ff60a33fe8a
-	0x7ff60a361005
-	0x7ff60a08d73e
-	0x7ff60a094e3f
-	0x7ff60a07b7e4
-	0x7ff60a07b99f
-	0x7ff60a061908
+	0x7ff7747ba235
+	0x7ff774512650
+	0x7ff7742a16dd
+	0x7ff7742fa27e
+	0x7ff7742fa58c
+	0x7ff77434ed77
+	0x7ff77434baba
+	0x7ff7742eb0ed
+	0x7ff7742ebf63
+	0x7ff7747e5d60
+	0x7ff7747dfe8a
+	0x7ff774801005
+	0x7ff77452d73e
+	0x7ff774534e3f
+	0x7ff77451b7e4
+	0x7ff77451b99f
+	0x7ff774501908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1192,23 +1192,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a31a235
-	0x7ff60a072650
-	0x7ff609e016dd
-	0x7ff609e5a27e
-	0x7ff609e5a58c
-	0x7ff609eaed77
-	0x7ff609eababa
-	0x7ff609e4b0ed
-	0x7ff609e4bf63
-	0x7ff60a345d60
-	0x7ff60a33fe8a
-	0x7ff60a361005
-	0x7ff60a08d73e
-	0x7ff60a094e3f
-	0x7ff60a07b7e4
-	0x7ff60a07b99f
-	0x7ff60a061908
+	0x7ff7747ba235
+	0x7ff774512650
+	0x7ff7742a16dd
+	0x7ff7742fa27e
+	0x7ff7742fa58c
+	0x7ff77434ed77
+	0x7ff77434baba
+	0x7ff7742eb0ed
+	0x7ff7742ebf63
+	0x7ff7747e5d60
+	0x7ff7747dfe8a
+	0x7ff774801005
+	0x7ff77452d73e
+	0x7ff774534e3f
+	0x7ff77451b7e4
+	0x7ff77451b99f
+	0x7ff774501908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1312,23 +1312,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a31a235
-	0x7ff60a072650
-	0x7ff609e016dd
-	0x7ff609e5a27e
-	0x7ff609e5a58c
-	0x7ff609eaed77
-	0x7ff609eababa
-	0x7ff609e4b0ed
-	0x7ff609e4bf63
-	0x7ff60a345d60
-	0x7ff60a33fe8a
-	0x7ff60a361005
-	0x7ff60a08d73e
-	0x7ff60a094e3f
-	0x7ff60a07b7e4
-	0x7ff60a07b99f
-	0x7ff60a061908
+	0x7ff7747ba235
+	0x7ff774512650
+	0x7ff7742a16dd
+	0x7ff7742fa27e
+	0x7ff7742fa58c
+	0x7ff77434ed77
+	0x7ff77434baba
+	0x7ff7742eb0ed
+	0x7ff7742ebf63
+	0x7ff7747e5d60
+	0x7ff7747dfe8a
+	0x7ff774801005
+	0x7ff77452d73e
+	0x7ff774534e3f
+	0x7ff77451b7e4
+	0x7ff77451b99f
+	0x7ff774501908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1432,23 +1432,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a31a235
-	0x7ff60a072650
-	0x7ff609e016dd
-	0x7ff609e5a27e
-	0x7ff609e5a58c
-	0x7ff609eaed77
-	0x7ff609eababa
-	0x7ff609e4b0ed
-	0x7ff609e4bf63
-	0x7ff60a345d60
-	0x7ff60a33fe8a
-	0x7ff60a361005
-	0x7ff60a08d73e
-	0x7ff60a094e3f
-	0x7ff60a07b7e4
-	0x7ff60a07b99f
-	0x7ff60a061908
+	0x7ff7747ba235
+	0x7ff774512650
+	0x7ff7742a16dd
+	0x7ff7742fa27e
+	0x7ff7742fa58c
+	0x7ff77434ed77
+	0x7ff77434baba
+	0x7ff7742eb0ed
+	0x7ff7742ebf63
+	0x7ff7747e5d60
+	0x7ff7747dfe8a
+	0x7ff774801005
+	0x7ff77452d73e
+	0x7ff774534e3f
+	0x7ff77451b7e4
+	0x7ff77451b99f
+	0x7ff774501908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1552,23 +1552,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a31a235
-	0x7ff60a072650
-	0x7ff609e016dd
-	0x7ff609e5a27e
-	0x7ff609e5a58c
-	0x7ff609eaed77
-	0x7ff609eababa
-	0x7ff609e4b0ed
-	0x7ff609e4bf63
-	0x7ff60a345d60
-	0x7ff60a33fe8a
-	0x7ff60a361005
-	0x7ff60a08d73e
-	0x7ff60a094e3f
-	0x7ff60a07b7e4
-	0x7ff60a07b99f
-	0x7ff60a061908
+	0x7ff7747ba235
+	0x7ff774512650
+	0x7ff7742a16dd
+	0x7ff7742fa27e
+	0x7ff7742fa58c
+	0x7ff77434ed77
+	0x7ff77434baba
+	0x7ff7742eb0ed
+	0x7ff7742ebf63
+	0x7ff7747e5d60
+	0x7ff7747dfe8a
+	0x7ff774801005
+	0x7ff77452d73e
+	0x7ff774534e3f
+	0x7ff77451b7e4
+	0x7ff77451b99f
+	0x7ff774501908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1672,23 +1672,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a31a235
-	0x7ff60a072650
-	0x7ff609e016dd
-	0x7ff609e5a27e
-	0x7ff609e5a58c
-	0x7ff609eaed77
-	0x7ff609eababa
-	0x7ff609e4b0ed
-	0x7ff609e4bf63
-	0x7ff60a345d60
-	0x7ff60a33fe8a
-	0x7ff60a361005
-	0x7ff60a08d73e
-	0x7ff60a094e3f
-	0x7ff60a07b7e4
-	0x7ff60a07b99f
-	0x7ff60a061908
+	0x7ff7747ba235
+	0x7ff774512650
+	0x7ff7742a16dd
+	0x7ff7742fa27e
+	0x7ff7742fa58c
+	0x7ff77434ed77
+	0x7ff77434baba
+	0x7ff7742eb0ed
+	0x7ff7742ebf63
+	0x7ff7747e5d60
+	0x7ff7747dfe8a
+	0x7ff774801005
+	0x7ff77452d73e
+	0x7ff774534e3f
+	0x7ff77451b7e4
+	0x7ff77451b99f
+	0x7ff774501908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1792,23 +1792,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a31a235
-	0x7ff60a072650
-	0x7ff609e016dd
-	0x7ff609e5a27e
-	0x7ff609e5a58c
-	0x7ff609eaed77
-	0x7ff609eababa
-	0x7ff609e4b0ed
-	0x7ff609e4bf63
-	0x7ff60a345d60
-	0x7ff60a33fe8a
-	0x7ff60a361005
-	0x7ff60a08d73e
-	0x7ff60a094e3f
-	0x7ff60a07b7e4
-	0x7ff60a07b99f
-	0x7ff60a061908
+	0x7ff7747ba235
+	0x7ff774512650
+	0x7ff7742a16dd
+	0x7ff7742fa27e
+	0x7ff7742fa58c
+	0x7ff77434ed77
+	0x7ff77434baba
+	0x7ff7742eb0ed
+	0x7ff7742ebf63
+	0x7ff7747e5d60
+	0x7ff7747dfe8a
+	0x7ff774801005
+	0x7ff77452d73e
+	0x7ff774534e3f
+	0x7ff77451b7e4
+	0x7ff77451b99f
+	0x7ff774501908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1912,23 +1912,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a31a235
-	0x7ff60a072650
-	0x7ff609e016dd
-	0x7ff609e5a27e
-	0x7ff609e5a58c
-	0x7ff609eaed77
-	0x7ff609eababa
-	0x7ff609e4b0ed
-	0x7ff609e4bf63
-	0x7ff60a345d60
-	0x7ff60a33fe8a
-	0x7ff60a361005
-	0x7ff60a08d73e
-	0x7ff60a094e3f
-	0x7ff60a07b7e4
-	0x7ff60a07b99f
-	0x7ff60a061908
+	0x7ff7747ba235
+	0x7ff774512650
+	0x7ff7742a16dd
+	0x7ff7742fa27e
+	0x7ff7742fa58c
+	0x7ff77434ed77
+	0x7ff77434baba
+	0x7ff7742eb0ed
+	0x7ff7742ebf63
+	0x7ff7747e5d60
+	0x7ff7747dfe8a
+	0x7ff774801005
+	0x7ff77452d73e
+	0x7ff774534e3f
+	0x7ff77451b7e4
+	0x7ff77451b99f
+	0x7ff774501908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2032,23 +2032,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a31a235
-	0x7ff60a072650
-	0x7ff609e016dd
-	0x7ff609e5a27e
-	0x7ff609e5a58c
-	0x7ff609eaed77
-	0x7ff609eababa
-	0x7ff609e4b0ed
-	0x7ff609e4bf63
-	0x7ff60a345d60
-	0x7ff60a33fe8a
-	0x7ff60a361005
-	0x7ff60a08d73e
-	0x7ff60a094e3f
-	0x7ff60a07b7e4
-	0x7ff60a07b99f
-	0x7ff60a061908
+	0x7ff7747ba235
+	0x7ff774512650
+	0x7ff7742a16dd
+	0x7ff7742fa27e
+	0x7ff7742fa58c
+	0x7ff77434ed77
+	0x7ff77434baba
+	0x7ff7742eb0ed
+	0x7ff7742ebf63
+	0x7ff7747e5d60
+	0x7ff7747dfe8a
+	0x7ff774801005
+	0x7ff77452d73e
+	0x7ff774534e3f
+	0x7ff77451b7e4
+	0x7ff77451b99f
+	0x7ff774501908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2152,23 +2152,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a31a235
-	0x7ff60a072650
-	0x7ff609e016dd
-	0x7ff609e5a27e
-	0x7ff609e5a58c
-	0x7ff609eaed77
-	0x7ff609eababa
-	0x7ff609e4b0ed
-	0x7ff609e4bf63
-	0x7ff60a345d60
-	0x7ff60a33fe8a
-	0x7ff60a361005
-	0x7ff60a08d73e
-	0x7ff60a094e3f
-	0x7ff60a07b7e4
-	0x7ff60a07b99f
-	0x7ff60a061908
+	0x7ff7747ba235
+	0x7ff774512650
+	0x7ff7742a16dd
+	0x7ff7742fa27e
+	0x7ff7742fa58c
+	0x7ff77434ed77
+	0x7ff77434baba
+	0x7ff7742eb0ed
+	0x7ff7742ebf63
+	0x7ff7747e5d60
+	0x7ff7747dfe8a
+	0x7ff774801005
+	0x7ff77452d73e
+	0x7ff774534e3f
+	0x7ff77451b7e4
+	0x7ff77451b99f
+	0x7ff774501908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2272,23 +2272,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a31a235
-	0x7ff60a072650
-	0x7ff609e016dd
-	0x7ff609e5a27e
-	0x7ff609e5a58c
-	0x7ff609eaed77
-	0x7ff609eababa
-	0x7ff609e4b0ed
-	0x7ff609e4bf63
-	0x7ff60a345d60
-	0x7ff60a33fe8a
-	0x7ff60a361005
-	0x7ff60a08d73e
-	0x7ff60a094e3f
-	0x7ff60a07b7e4
-	0x7ff60a07b99f
-	0x7ff60a061908
+	0x7ff7747ba235
+	0x7ff774512650
+	0x7ff7742a16dd
+	0x7ff7742fa27e
+	0x7ff7742fa58c
+	0x7ff77434ed77
+	0x7ff77434baba
+	0x7ff7742eb0ed
+	0x7ff7742ebf63
+	0x7ff7747e5d60
+	0x7ff7747dfe8a
+	0x7ff774801005
+	0x7ff77452d73e
+	0x7ff774534e3f
+	0x7ff77451b7e4
+	0x7ff77451b99f
+	0x7ff774501908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2489,23 +2489,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a31a235
-	0x7ff60a072650
-	0x7ff609e016dd
-	0x7ff609e5a27e
-	0x7ff609e5a58c
-	0x7ff609eaed77
-	0x7ff609eababa
-	0x7ff609e4b0ed
-	0x7ff609e4bf63
-	0x7ff60a345d60
-	0x7ff60a33fe8a
-	0x7ff60a361005
-	0x7ff60a08d73e
-	0x7ff60a094e3f
-	0x7ff60a07b7e4
-	0x7ff60a07b99f
-	0x7ff60a061908
+	0x7ff7747ba235
+	0x7ff774512650
+	0x7ff7742a16dd
+	0x7ff7742fa27e
+	0x7ff7742fa58c
+	0x7ff77434ed77
+	0x7ff77434baba
+	0x7ff7742eb0ed
+	0x7ff7742ebf63
+	0x7ff7747e5d60
+	0x7ff7747dfe8a
+	0x7ff774801005
+	0x7ff77452d73e
+	0x7ff774534e3f
+	0x7ff77451b7e4
+	0x7ff77451b99f
+	0x7ff774501908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2609,23 +2609,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a31a235
-	0x7ff60a072650
-	0x7ff609e016dd
-	0x7ff609e5a27e
-	0x7ff609e5a58c
-	0x7ff609eaed77
-	0x7ff609eababa
-	0x7ff609e4b0ed
-	0x7ff609e4bf63
-	0x7ff60a345d60
-	0x7ff60a33fe8a
-	0x7ff60a361005
-	0x7ff60a08d73e
-	0x7ff60a094e3f
-	0x7ff60a07b7e4
-	0x7ff60a07b99f
-	0x7ff60a061908
+	0x7ff7747ba235
+	0x7ff774512650
+	0x7ff7742a16dd
+	0x7ff7742fa27e
+	0x7ff7742fa58c
+	0x7ff77434ed77
+	0x7ff77434baba
+	0x7ff7742eb0ed
+	0x7ff7742ebf63
+	0x7ff7747e5d60
+	0x7ff7747dfe8a
+	0x7ff774801005
+	0x7ff77452d73e
+	0x7ff774534e3f
+	0x7ff77451b7e4
+	0x7ff77451b99f
+	0x7ff774501908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2729,23 +2729,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a31a235
-	0x7ff60a072650
-	0x7ff609e016dd
-	0x7ff609e5a27e
-	0x7ff609e5a58c
-	0x7ff609eaed77
-	0x7ff609eababa
-	0x7ff609e4b0ed
-	0x7ff609e4bf63
-	0x7ff60a345d60
-	0x7ff60a33fe8a
-	0x7ff60a361005
-	0x7ff60a08d73e
-	0x7ff60a094e3f
-	0x7ff60a07b7e4
-	0x7ff60a07b99f
-	0x7ff60a061908
+	0x7ff7747ba235
+	0x7ff774512650
+	0x7ff7742a16dd
+	0x7ff7742fa27e
+	0x7ff7742fa58c
+	0x7ff77434ed77
+	0x7ff77434baba
+	0x7ff7742eb0ed
+	0x7ff7742ebf63
+	0x7ff7747e5d60
+	0x7ff7747dfe8a
+	0x7ff774801005
+	0x7ff77452d73e
+	0x7ff774534e3f
+	0x7ff77451b7e4
+	0x7ff77451b99f
+	0x7ff774501908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2849,23 +2849,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a31a235
-	0x7ff60a072650
-	0x7ff609e016dd
-	0x7ff609e5a27e
-	0x7ff609e5a58c
-	0x7ff609eaed77
-	0x7ff609eababa
-	0x7ff609e4b0ed
-	0x7ff609e4bf63
-	0x7ff60a345d60
-	0x7ff60a33fe8a
-	0x7ff60a361005
-	0x7ff60a08d73e
-	0x7ff60a094e3f
-	0x7ff60a07b7e4
-	0x7ff60a07b99f
-	0x7ff60a061908
+	0x7ff7747ba235
+	0x7ff774512650
+	0x7ff7742a16dd
+	0x7ff7742fa27e
+	0x7ff7742fa58c
+	0x7ff77434ed77
+	0x7ff77434baba
+	0x7ff7742eb0ed
+	0x7ff7742ebf63
+	0x7ff7747e5d60
+	0x7ff7747dfe8a
+	0x7ff774801005
+	0x7ff77452d73e
+	0x7ff774534e3f
+	0x7ff77451b7e4
+	0x7ff77451b99f
+	0x7ff774501908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2969,23 +2969,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a31a235
-	0x7ff60a072650
-	0x7ff609e016dd
-	0x7ff609e5a27e
-	0x7ff609e5a58c
-	0x7ff609eaed77
-	0x7ff609eababa
-	0x7ff609e4b0ed
-	0x7ff609e4bf63
-	0x7ff60a345d60
-	0x7ff60a33fe8a
-	0x7ff60a361005
-	0x7ff60a08d73e
-	0x7ff60a094e3f
-	0x7ff60a07b7e4
-	0x7ff60a07b99f
-	0x7ff60a061908
+	0x7ff7747ba235
+	0x7ff774512650
+	0x7ff7742a16dd
+	0x7ff7742fa27e
+	0x7ff7742fa58c
+	0x7ff77434ed77
+	0x7ff77434baba
+	0x7ff7742eb0ed
+	0x7ff7742ebf63
+	0x7ff7747e5d60
+	0x7ff7747dfe8a
+	0x7ff774801005
+	0x7ff77452d73e
+	0x7ff774534e3f
+	0x7ff77451b7e4
+	0x7ff77451b99f
+	0x7ff774501908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3089,23 +3089,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a31a235
-	0x7ff60a072650
-	0x7ff609e016dd
-	0x7ff609e5a27e
-	0x7ff609e5a58c
-	0x7ff609eaed77
-	0x7ff609eababa
-	0x7ff609e4b0ed
-	0x7ff609e4bf63
-	0x7ff60a345d60
-	0x7ff60a33fe8a
-	0x7ff60a361005
-	0x7ff60a08d73e
-	0x7ff60a094e3f
-	0x7ff60a07b7e4
-	0x7ff60a07b99f
-	0x7ff60a061908
+	0x7ff7747ba235
+	0x7ff774512650
+	0x7ff7742a16dd
+	0x7ff7742fa27e
+	0x7ff7742fa58c
+	0x7ff77434ed77
+	0x7ff77434baba
+	0x7ff7742eb0ed
+	0x7ff7742ebf63
+	0x7ff7747e5d60
+	0x7ff7747dfe8a
+	0x7ff774801005
+	0x7ff77452d73e
+	0x7ff774534e3f
+	0x7ff77451b7e4
+	0x7ff77451b99f
+	0x7ff774501908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3209,23 +3209,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a31a235
-	0x7ff60a072650
-	0x7ff609e016dd
-	0x7ff609e5a27e
-	0x7ff609e5a58c
-	0x7ff609eaed77
-	0x7ff609eababa
-	0x7ff609e4b0ed
-	0x7ff609e4bf63
-	0x7ff60a345d60
-	0x7ff60a33fe8a
-	0x7ff60a361005
-	0x7ff60a08d73e
-	0x7ff60a094e3f
-	0x7ff60a07b7e4
-	0x7ff60a07b99f
-	0x7ff60a061908
+	0x7ff7747ba235
+	0x7ff774512650
+	0x7ff7742a16dd
+	0x7ff7742fa27e
+	0x7ff7742fa58c
+	0x7ff77434ed77
+	0x7ff77434baba
+	0x7ff7742eb0ed
+	0x7ff7742ebf63
+	0x7ff7747e5d60
+	0x7ff7747dfe8a
+	0x7ff774801005
+	0x7ff77452d73e
+	0x7ff774534e3f
+	0x7ff77451b7e4
+	0x7ff77451b99f
+	0x7ff774501908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3329,23 +3329,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a31a235
-	0x7ff60a072650
-	0x7ff609e016dd
-	0x7ff609e5a27e
-	0x7ff609e5a58c
-	0x7ff609eaed77
-	0x7ff609eababa
-	0x7ff609e4b0ed
-	0x7ff609e4bf63
-	0x7ff60a345d60
-	0x7ff60a33fe8a
-	0x7ff60a361005
-	0x7ff60a08d73e
-	0x7ff60a094e3f
-	0x7ff60a07b7e4
-	0x7ff60a07b99f
-	0x7ff60a061908
+	0x7ff7747ba235
+	0x7ff774512650
+	0x7ff7742a16dd
+	0x7ff7742fa27e
+	0x7ff7742fa58c
+	0x7ff77434ed77
+	0x7ff77434baba
+	0x7ff7742eb0ed
+	0x7ff7742ebf63
+	0x7ff7747e5d60
+	0x7ff7747dfe8a
+	0x7ff774801005
+	0x7ff77452d73e
+	0x7ff774534e3f
+	0x7ff77451b7e4
+	0x7ff77451b99f
+	0x7ff774501908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3449,23 +3449,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff60a31a235
-	0x7ff60a072650
-	0x7ff609e016dd
-	0x7ff609e5a27e
-	0x7ff609e5a58c
-	0x7ff609eaed77
-	0x7ff609eababa
-	0x7ff609e4b0ed
-	0x7ff609e4bf63
-	0x7ff60a345d60
-	0x7ff60a33fe8a
-	0x7ff60a361005
-	0x7ff60a08d73e
-	0x7ff60a094e3f
-	0x7ff60a07b7e4
-	0x7ff60a07b99f
-	0x7ff60a061908
+	0x7ff7747ba235
+	0x7ff774512650
+	0x7ff7742a16dd
+	0x7ff7742fa27e
+	0x7ff7742fa58c
+	0x7ff77434ed77
+	0x7ff77434baba
+	0x7ff7742eb0ed
+	0x7ff7742ebf63
+	0x7ff7747e5d60
+	0x7ff7747dfe8a
+	0x7ff774801005
+	0x7ff77452d73e
+	0x7ff774534e3f
+	0x7ff77451b7e4
+	0x7ff77451b99f
+	0x7ff774501908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
